--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
   <si>
     <t>Mat</t>
   </si>
@@ -82,160 +82,124 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ATZIN HEFZIBA</t>
@@ -250,73 +214,55 @@
     <t>AMISADAI</t>
   </si>
   <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>MAGDA SARAY</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>HARUMI</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
-    <t>CRISTOPHER</t>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>TAURINO</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>HARUMI</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
     <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -912,16 +858,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.42</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -935,16 +884,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -958,16 +910,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -981,16 +936,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1004,16 +962,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1027,16 +988,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>63.41</v>
+      </c>
+      <c r="H7">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1092,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>61.29</v>
+        <v>77.42</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1118,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1153,7 +1117,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1170,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1196,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>78.56999999999999</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1231,7 +1195,7 @@
         <v>63.41</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,16 +1237,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920163</v>
+        <v>21330051920166</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1296,22 +1260,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1319,22 +1283,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920176</v>
+        <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1342,22 +1306,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920253</v>
+        <v>21330051920149</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1365,22 +1329,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>21330051920298</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1388,22 +1352,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920149</v>
+        <v>21330051920337</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1411,16 +1375,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920298</v>
+        <v>21330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1434,16 +1398,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920299</v>
+        <v>21330051920328</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1457,114 +1421,114 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920337</v>
+        <v>21330051920257</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920316</v>
+        <v>21330051920358</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920321</v>
+        <v>21330051920286</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920323</v>
+        <v>21330051920353</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920170</v>
+        <v>21330051920239</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1572,22 +1536,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920181</v>
+        <v>21330051920249</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1595,22 +1559,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920257</v>
+        <v>21330051920223</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1618,22 +1582,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920358</v>
+        <v>21330051920293</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1641,22 +1605,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920286</v>
+        <v>21330051920299</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1664,22 +1628,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920358</v>
+        <v>21330051920300</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1687,22 +1651,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920353</v>
+        <v>21330051920305</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1710,22 +1674,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920218</v>
+        <v>21330051920313</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1733,22 +1697,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920219</v>
+        <v>21330051920316</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1756,22 +1720,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920239</v>
+        <v>21330051920319</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1779,208 +1743,24 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920249</v>
+        <v>21330051920326</v>
       </c>
       <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
         <v>39</v>
       </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920223</v>
-      </c>
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920293</v>
-      </c>
-      <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920300</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920305</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920310</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920311</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920313</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920319</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -88,24 +88,21 @@
     <t>ARGÜELLO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -148,24 +145,21 @@
     <t>NARANJO</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -205,25 +199,22 @@
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
     <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1205,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1243,10 +1234,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1266,10 +1257,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1283,16 +1274,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>21330051920257</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1312,10 +1303,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1335,10 +1326,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1358,10 +1349,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1381,10 +1372,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1398,39 +1389,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920328</v>
+        <v>21330051920088</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920257</v>
+        <v>21330051920358</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1444,16 +1435,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1467,22 +1458,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920286</v>
+        <v>21330051920353</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1490,22 +1481,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920353</v>
+        <v>21330051920239</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1513,16 +1504,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920239</v>
+        <v>21330051920249</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1536,16 +1527,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920249</v>
+        <v>21330051920223</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1559,22 +1550,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920223</v>
+        <v>21330051920293</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1582,16 +1573,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920293</v>
+        <v>21330051920299</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1605,16 +1596,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920299</v>
+        <v>21330051920300</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1628,16 +1619,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920300</v>
+        <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1651,16 +1642,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920305</v>
+        <v>21330051920313</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1674,16 +1665,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920313</v>
+        <v>21330051920316</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1697,16 +1688,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920316</v>
+        <v>21330051920319</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1720,16 +1711,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920319</v>
+        <v>21330051920326</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1738,29 +1729,6 @@
         <v>14</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920326</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,12 @@
     <t>MACARIO</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
@@ -194,6 +200,12 @@
   </si>
   <si>
     <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
   </si>
   <si>
     <t>ATZIN HEFZIBA</t>
@@ -1196,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,10 +1246,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1251,22 +1263,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920253</v>
+        <v>21330051920171</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1274,22 +1286,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920257</v>
+        <v>21330051920175</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1297,7 +1309,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920149</v>
+        <v>21330051920253</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1306,13 +1318,13 @@
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1320,7 +1332,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920298</v>
+        <v>21330051920257</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1329,13 +1341,13 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1343,22 +1355,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920337</v>
+        <v>21330051920149</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1366,16 +1378,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920321</v>
+        <v>21330051920298</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1389,53 +1401,53 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920088</v>
+        <v>21330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920358</v>
+        <v>21330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920286</v>
+        <v>21330051920088</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1444,7 +1456,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1458,7 +1470,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920353</v>
+        <v>21330051920358</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1467,13 +1479,13 @@
         <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1481,7 +1493,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920239</v>
+        <v>21330051920286</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1490,13 +1502,13 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1504,7 +1516,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920249</v>
+        <v>21330051920353</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1513,13 +1525,13 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1527,7 +1539,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920223</v>
+        <v>21330051920239</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -1536,7 +1548,7 @@
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1550,7 +1562,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920293</v>
+        <v>21330051920249</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1559,13 +1571,13 @@
         <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1573,22 +1585,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920299</v>
+        <v>21330051920223</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1596,16 +1608,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920300</v>
+        <v>21330051920293</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1619,16 +1631,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920305</v>
+        <v>21330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1642,16 +1654,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920313</v>
+        <v>21330051920300</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1665,7 +1677,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920316</v>
+        <v>21330051920305</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -1674,7 +1686,7 @@
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1688,16 +1700,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920319</v>
+        <v>21330051920313</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1711,16 +1723,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920326</v>
+        <v>21330051920316</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1729,6 +1741,52 @@
         <v>14</v>
       </c>
       <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920319</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920326</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -100,6 +100,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>DOLORES</t>
   </si>
   <si>
@@ -115,9 +118,6 @@
     <t>VARGAS</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>MADRIGAL</t>
   </si>
   <si>
@@ -157,6 +157,9 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -172,9 +175,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -217,6 +217,9 @@
     <t>JOSELIN</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>AMISADAI</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
   </si>
   <si>
     <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
   <si>
     <t>AMERICA PAOLA</t>
@@ -1269,7 +1269,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920298</v>
+        <v>21330051920353</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920337</v>
+        <v>21330051920298</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>67</v>
@@ -1424,13 +1424,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920321</v>
+        <v>21330051920337</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>68</v>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920088</v>
+        <v>21330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
@@ -1462,15 +1462,15 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920358</v>
+        <v>21330051920088</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920286</v>
+        <v>21330051920358</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920353</v>
+        <v>21330051920286</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1634,10 +1634,10 @@
         <v>21330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>77</v>
@@ -1752,7 +1752,7 @@
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>81</v>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -82,42 +82,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
     <t>MADRIGAL</t>
   </si>
   <si>
@@ -127,6 +127,9 @@
     <t>ZACAMECAHUA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -145,7 +148,19 @@
     <t>SOLIS</t>
   </si>
   <si>
-    <t>NERI</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
   </si>
   <si>
     <t>NARANJO</t>
@@ -154,90 +169,84 @@
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>CORONA</t>
   </si>
   <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
     <t>YAHIR</t>
   </si>
   <si>
     <t>JHOSUA LEVY</t>
   </si>
   <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>JOSELIN</t>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>MAGDA SARAY</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
     <t>AMERICA PAOLA</t>
   </si>
   <si>
@@ -247,10 +256,10 @@
     <t>HARUMI</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
   </si>
   <si>
     <t>AMY JULIET</t>
@@ -1208,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,16 +1249,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920166</v>
+        <v>21330051920171</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1263,16 +1272,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1286,22 +1295,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920175</v>
+        <v>21330051920149</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1309,22 +1318,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920253</v>
+        <v>21330051920386</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1332,22 +1341,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920257</v>
+        <v>21330051920199</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1355,22 +1364,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920149</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1378,22 +1387,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920353</v>
+        <v>21330051920337</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1401,16 +1410,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920298</v>
+        <v>21330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1424,48 +1433,48 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920337</v>
+        <v>21330051920253</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920321</v>
+        <v>21330051920257</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1476,10 +1485,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1496,13 +1505,13 @@
         <v>21330051920358</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1519,13 +1528,13 @@
         <v>21330051920286</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1539,22 +1548,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920239</v>
+        <v>21330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1562,16 +1571,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920249</v>
+        <v>21330051920239</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1585,16 +1594,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920223</v>
+        <v>21330051920249</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1608,22 +1617,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920293</v>
+        <v>21330051920223</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1631,22 +1640,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920299</v>
+        <v>19330061430023</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1654,16 +1663,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920300</v>
+        <v>21330051920293</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1677,16 +1686,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920305</v>
+        <v>21330051920300</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1700,7 +1709,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920313</v>
+        <v>21330051920305</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -1709,7 +1718,7 @@
         <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1723,7 +1732,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920316</v>
+        <v>21330051920313</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
@@ -1732,7 +1741,7 @@
         <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1746,16 +1755,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920319</v>
+        <v>21330051920316</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1769,16 +1778,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920326</v>
+        <v>21330051920319</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1787,6 +1796,29 @@
         <v>14</v>
       </c>
       <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920326</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
   <si>
     <t>Mat</t>
   </si>
@@ -118,12 +118,6 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
     <t>ZACAMECAHUA</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
@@ -245,12 +236,6 @@
   </si>
   <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
   </si>
   <si>
     <t>HARUMI</t>
@@ -1146,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -1217,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,7 +1243,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1278,10 +1263,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1301,10 +1286,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1324,10 +1309,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1347,10 +1332,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1370,10 +1355,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1393,10 +1378,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1416,10 +1401,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1439,10 +1424,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1462,10 +1447,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1485,10 +1470,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1508,10 +1493,10 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1531,10 +1516,10 @@
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1554,10 +1539,10 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1571,16 +1556,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920239</v>
+        <v>21330051920223</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1594,22 +1579,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920249</v>
+        <v>19330061430023</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1617,22 +1602,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920223</v>
+        <v>21330051920293</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1640,22 +1625,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330061430023</v>
+        <v>21330051920300</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1663,16 +1648,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920293</v>
+        <v>21330051920305</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1686,16 +1671,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920300</v>
+        <v>21330051920313</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1709,16 +1694,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920305</v>
+        <v>21330051920316</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1732,16 +1717,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920313</v>
+        <v>21330051920319</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1755,16 +1740,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920316</v>
+        <v>21330051920326</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1773,52 +1758,6 @@
         <v>14</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920319</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920326</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -82,184 +82,91 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
+    <t>ARGÜELLO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
     <t>TZOPITL</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
     <t>NEGRETE</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>YAHIR</t>
   </si>
   <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
     <t>HARUMI</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
     <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1053,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>77.42</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1079,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>82.93000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1105,13 +1012,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -1131,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>86.84</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -1157,16 +1064,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1183,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>63.41</v>
+        <v>78.05</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,16 +1141,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1257,22 +1164,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920175</v>
+        <v>21330051920149</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1280,22 +1187,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920149</v>
+        <v>21330051920323</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1303,137 +1210,137 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920386</v>
+        <v>21330051920171</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920199</v>
+        <v>21330051920253</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>21330051920358</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920337</v>
+        <v>21330051920223</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920321</v>
+        <v>19330061430023</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920253</v>
+        <v>21330051920305</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1441,323 +1348,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920257</v>
+        <v>21330051920319</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920088</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920358</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920286</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920353</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920223</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330061430023</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920293</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920300</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920305</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920313</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920316</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920319</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920326</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>
